--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.90.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.90.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.90.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.90.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -601,19 +601,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 880.â€�</t>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ï»¿PROCEEDINGS TO HEAR CAUSE Â« PRO CONFESSO.â€�</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE « PRO CONFESSO.”</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE « PRO CONFESSO.”</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 83</t>
+          <t>L20: symbol-only separator/garbage line :: 880.”</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -630,7 +634,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L53: line starts with digit/letter garbage token | suspicious token(s): 1in (letter/digit mix) :: 1in En-</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • imme-</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -665,12 +669,16 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ imme-</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • imme-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
-      <c r="N3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>L34: isolated marker/symbol line :: 83</t>
+        </is>
+      </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
           <t>L43: isolated marker/symbol line :: :</t>
@@ -679,7 +687,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L53: line starts with digit/letter garbage token | suspicious token(s): 1in (letter/digit mix) :: 1in En-</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -713,7 +725,11 @@
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="1" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
+        </is>
+      </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
           <t>L45: isolated marker/symbol line :: *</t>
@@ -738,7 +754,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -985,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1019,7 +1035,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1102,7 +1118,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
